--- a/main/StructureDefinition-Idat.xlsx
+++ b/main/StructureDefinition-Idat.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-18</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/main/StructureDefinition-Idat.xlsx
+++ b/main/StructureDefinition-Idat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -490,25 +490,29 @@
     <t>The registered place of birth of the patient. A sytem may use the address.text if they don't store the birthPlace address in discrete elements.</t>
   </si>
   <si>
-    <t>Patient.extension:birthPlace.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:birthPlace.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -558,24 +562,16 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Patient.extension:birthPlace.value[x].id</t>
   </si>
   <si>
     <t>Patient.extension.value[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].extension</t>
@@ -912,9 +908,6 @@
     <t>Patient.extension:nationality.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Patient.extension:nationality.extension:code</t>
   </si>
   <si>
@@ -1198,7 +1191,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -3732,7 +3725,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3755,10 +3748,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3781,13 +3774,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3838,7 +3831,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3847,13 +3840,13 @@
         <v>90</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>21</v>
@@ -3870,10 +3863,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3944,7 +3937,7 @@
         <v>138</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>21</v>
@@ -3953,7 +3946,7 @@
         <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3985,10 +3978,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4014,13 +4007,13 @@
         <v>104</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4028,7 +4021,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>21</v>
@@ -4070,7 +4063,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -4102,10 +4095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4128,13 +4121,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4185,7 +4178,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4194,7 +4187,7 @@
         <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>102</v>
@@ -4243,13 +4236,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4300,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4315,7 +4308,7 @@
         <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
@@ -4332,14 +4325,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4361,13 +4354,13 @@
         <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4408,7 +4401,7 @@
         <v>138</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
@@ -4417,7 +4410,7 @@
         <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4432,7 +4425,7 @@
         <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
@@ -4449,10 +4442,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4478,16 +4471,16 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -4500,43 +4493,43 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="U17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4551,16 +4544,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4568,10 +4561,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4597,13 +4590,13 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4617,43 +4610,43 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="U18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4668,7 +4661,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
@@ -4677,7 +4670,7 @@
         <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4685,10 +4678,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4711,19 +4704,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4736,43 +4729,43 @@
         <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4787,16 +4780,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4804,10 +4797,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4830,13 +4823,13 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4851,43 +4844,43 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4902,16 +4895,16 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4919,14 +4912,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4945,13 +4938,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4966,43 +4959,43 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5017,16 +5010,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -5034,14 +5027,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5060,16 +5053,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5083,43 +5076,43 @@
         <v>21</v>
       </c>
       <c r="T22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5134,16 +5127,16 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>21</v>
@@ -5151,14 +5144,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5177,13 +5170,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5234,7 +5227,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5249,16 +5242,16 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>21</v>
@@ -5266,14 +5259,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5292,13 +5285,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5313,43 +5306,43 @@
         <v>21</v>
       </c>
       <c r="T24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5364,16 +5357,16 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>21</v>
@@ -5381,10 +5374,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5407,16 +5400,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5466,7 +5459,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5481,16 +5474,16 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>21</v>
@@ -5498,10 +5491,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5524,17 +5517,17 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5547,43 +5540,43 @@
         <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5598,16 +5591,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -5615,13 +5608,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
@@ -5643,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5709,7 +5702,7 @@
         <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>141</v>
@@ -5732,10 +5725,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5758,13 +5751,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5815,7 +5808,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5824,13 +5817,13 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -5847,14 +5840,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5876,13 +5869,13 @@
         <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="N29" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5923,7 +5916,7 @@
         <v>138</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
@@ -5932,7 +5925,7 @@
         <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5947,7 +5940,7 @@
         <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -5964,13 +5957,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>21</v>
@@ -6049,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6081,10 +6074,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6107,13 +6100,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6164,7 +6157,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6173,13 +6166,13 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
@@ -6196,10 +6189,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6270,7 +6263,7 @@
         <v>138</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
@@ -6279,7 +6272,7 @@
         <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6311,10 +6304,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6340,13 +6333,13 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6354,7 +6347,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>21</v>
@@ -6396,7 +6389,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6428,10 +6421,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6454,13 +6447,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6487,11 +6480,11 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6509,7 +6502,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6518,7 +6511,7 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
@@ -6541,10 +6534,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6567,13 +6560,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6624,7 +6617,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6639,7 +6632,7 @@
         <v>21</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -6656,14 +6649,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6685,13 +6678,13 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6732,7 +6725,7 @@
         <v>138</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>21</v>
@@ -6741,7 +6734,7 @@
         <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6756,7 +6749,7 @@
         <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
@@ -6773,10 +6766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6799,19 +6792,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6860,7 +6853,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6875,7 +6868,7 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -6884,7 +6877,7 @@
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6892,10 +6885,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6918,13 +6911,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6975,7 +6968,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6990,7 +6983,7 @@
         <v>21</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
@@ -7007,14 +7000,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7036,13 +7029,13 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7083,7 +7076,7 @@
         <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
@@ -7092,7 +7085,7 @@
         <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7107,7 +7100,7 @@
         <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -7124,10 +7117,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7153,16 +7146,16 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7211,7 +7204,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7226,7 +7219,7 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -7235,7 +7228,7 @@
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -7243,10 +7236,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7269,16 +7262,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7328,7 +7321,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7343,7 +7336,7 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -7352,7 +7345,7 @@
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -7360,10 +7353,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7389,14 +7382,14 @@
         <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -7445,7 +7438,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7460,7 +7453,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -7469,7 +7462,7 @@
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7477,10 +7470,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7503,17 +7496,17 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7562,7 +7555,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7577,7 +7570,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -7586,7 +7579,7 @@
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -7594,10 +7587,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7620,19 +7613,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7681,7 +7674,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7696,7 +7689,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -7705,7 +7698,7 @@
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7713,10 +7706,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7739,19 +7732,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7800,7 +7793,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7815,7 +7808,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -7824,7 +7817,7 @@
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7832,13 +7825,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
@@ -7863,10 +7856,10 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7917,7 +7910,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7949,10 +7942,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7975,13 +7968,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8032,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8041,13 +8034,13 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -8064,10 +8057,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8138,7 +8131,7 @@
         <v>138</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>21</v>
@@ -8147,7 +8140,7 @@
         <v>139</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8179,10 +8172,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8208,13 +8201,13 @@
         <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8222,7 +8215,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -8264,7 +8257,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -8296,10 +8289,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8322,13 +8315,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8379,7 +8372,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8388,7 +8381,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -8411,10 +8404,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8440,13 +8433,13 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8454,7 +8447,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>21</v>
@@ -8496,7 +8489,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>90</v>
@@ -8528,10 +8521,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8554,13 +8547,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8611,7 +8604,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8613,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8643,14 +8636,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8672,16 +8665,16 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8730,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8762,10 +8755,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8788,17 +8781,17 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8847,7 +8840,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8862,16 +8855,16 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>21</v>
@@ -8879,10 +8872,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8905,26 +8898,26 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q55" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="R55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8968,7 +8961,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8983,13 +8976,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -9000,10 +8993,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9026,19 +9019,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -9087,7 +9080,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9102,16 +9095,16 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -9119,10 +9112,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9145,13 +9138,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9202,7 +9195,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9217,7 +9210,7 @@
         <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -9234,14 +9227,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9263,13 +9256,13 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9310,7 +9303,7 @@
         <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
@@ -9319,7 +9312,7 @@
         <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9334,7 +9327,7 @@
         <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -9351,10 +9344,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9380,16 +9373,16 @@
         <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9414,31 +9407,31 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9453,7 +9446,7 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
@@ -9462,7 +9455,7 @@
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9470,10 +9463,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9496,19 +9489,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9557,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9572,7 +9565,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
@@ -9581,7 +9574,7 @@
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9589,14 +9582,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9615,16 +9608,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9674,7 +9667,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9689,7 +9682,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
@@ -9698,7 +9691,7 @@
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9706,14 +9699,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9732,16 +9725,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9791,7 +9784,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9806,7 +9799,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -9815,7 +9808,7 @@
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9823,10 +9816,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9849,13 +9842,13 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9906,7 +9899,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9921,7 +9914,7 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
@@ -9930,7 +9923,7 @@
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9938,10 +9931,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9964,13 +9957,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10021,7 +10014,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10053,10 +10046,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10134,7 +10127,7 @@
         <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10166,13 +10159,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -10194,16 +10187,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10253,7 +10246,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10262,13 +10255,13 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
@@ -10285,10 +10278,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10311,13 +10304,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10368,7 +10361,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10377,13 +10370,13 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
@@ -10400,10 +10393,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10474,7 +10467,7 @@
         <v>138</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
@@ -10483,7 +10476,7 @@
         <v>139</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10515,10 +10508,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10544,13 +10537,13 @@
         <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10558,7 +10551,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>21</v>
@@ -10600,7 +10593,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -10632,10 +10625,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10661,10 +10654,10 @@
         <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10673,7 +10666,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>21</v>
@@ -10691,11 +10684,11 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10713,7 +10706,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10722,7 +10715,7 @@
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>102</v>
@@ -10745,10 +10738,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10771,13 +10764,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10801,7 +10794,7 @@
         <v>21</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="X71" t="s" s="2">
         <v>21</v>
@@ -10828,7 +10821,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10860,10 +10853,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10886,13 +10879,13 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10943,7 +10936,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10958,7 +10951,7 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -10967,7 +10960,7 @@
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
@@ -10975,10 +10968,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11001,17 +10994,17 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11060,7 +11053,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11075,7 +11068,7 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
@@ -11084,7 +11077,7 @@
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -11092,10 +11085,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11118,19 +11111,19 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -11179,7 +11172,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11194,16 +11187,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>21</v>
@@ -11211,10 +11204,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11240,16 +11233,16 @@
         <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11274,13 +11267,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -11298,7 +11291,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11313,16 +11306,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>21</v>
@@ -11330,10 +11323,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11356,19 +11349,19 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -11417,7 +11410,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11432,27 +11425,27 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11475,19 +11468,19 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11536,7 +11529,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11551,16 +11544,16 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11568,10 +11561,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11594,19 +11587,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11655,7 +11648,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11670,16 +11663,16 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>21</v>
@@ -11687,10 +11680,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11713,13 +11706,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11770,7 +11763,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11785,7 +11778,7 @@
         <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
@@ -11802,14 +11795,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11831,13 +11824,13 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11878,7 +11871,7 @@
         <v>138</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
@@ -11887,7 +11880,7 @@
         <v>139</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11902,7 +11895,7 @@
         <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>21</v>
@@ -11919,10 +11912,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11948,16 +11941,16 @@
         <v>110</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11970,43 +11963,43 @@
         <v>21</v>
       </c>
       <c r="T81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
+      <c r="Y81" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y81" t="s" s="2">
+      <c r="Z81" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Z81" t="s" s="2">
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12021,16 +12014,16 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>21</v>
@@ -12038,10 +12031,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12067,13 +12060,13 @@
         <v>110</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12087,43 +12080,43 @@
         <v>21</v>
       </c>
       <c r="T82" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y82" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y82" t="s" s="2">
+      <c r="Z82" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12138,7 +12131,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -12147,7 +12140,7 @@
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>21</v>
@@ -12155,10 +12148,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12181,19 +12174,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12206,43 +12199,43 @@
         <v>21</v>
       </c>
       <c r="T83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12257,16 +12250,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>21</v>
@@ -12274,10 +12267,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12300,13 +12293,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12321,43 +12314,43 @@
         <v>21</v>
       </c>
       <c r="T84" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12372,16 +12365,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>21</v>
@@ -12389,14 +12382,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12415,13 +12408,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12436,43 +12429,43 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12487,16 +12480,16 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>21</v>
@@ -12504,14 +12497,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12530,16 +12523,16 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12553,43 +12546,43 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12604,16 +12597,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>21</v>
@@ -12621,14 +12614,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12647,13 +12640,13 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12704,7 +12697,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12719,16 +12712,16 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>21</v>
@@ -12736,14 +12729,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12762,13 +12755,13 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12783,43 +12776,43 @@
         <v>21</v>
       </c>
       <c r="T88" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12834,16 +12827,16 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>21</v>
@@ -12851,10 +12844,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12877,16 +12870,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12936,7 +12929,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12951,16 +12944,16 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>21</v>
@@ -12968,10 +12961,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12994,17 +12987,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13017,43 +13010,43 @@
         <v>21</v>
       </c>
       <c r="T90" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13068,16 +13061,16 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>21</v>
@@ -13085,10 +13078,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13111,17 +13104,17 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -13146,13 +13139,13 @@
         <v>21</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -13170,7 +13163,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13185,16 +13178,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13202,10 +13195,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13228,13 +13221,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13285,7 +13278,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13300,7 +13293,7 @@
         <v>21</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -13317,14 +13310,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13346,13 +13339,13 @@
         <v>135</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13393,7 +13386,7 @@
         <v>138</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>21</v>
@@ -13402,7 +13395,7 @@
         <v>139</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13417,7 +13410,7 @@
         <v>141</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -13434,10 +13427,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13460,19 +13453,19 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -13521,7 +13514,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13536,7 +13529,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
@@ -13545,7 +13538,7 @@
         <v>21</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -13553,10 +13546,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13579,13 +13572,13 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13636,7 +13629,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13651,7 +13644,7 @@
         <v>21</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
@@ -13668,14 +13661,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13697,13 +13690,13 @@
         <v>135</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13744,7 +13737,7 @@
         <v>138</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>21</v>
@@ -13753,7 +13746,7 @@
         <v>139</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13768,7 +13761,7 @@
         <v>141</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -13785,10 +13778,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13814,16 +13807,16 @@
         <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -13872,7 +13865,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13887,7 +13880,7 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>21</v>
@@ -13896,7 +13889,7 @@
         <v>21</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>21</v>
@@ -13904,10 +13897,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13930,16 +13923,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13989,7 +13982,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14004,7 +13997,7 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>21</v>
@@ -14013,7 +14006,7 @@
         <v>21</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>21</v>
@@ -14021,10 +14014,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14050,14 +14043,14 @@
         <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -14106,7 +14099,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14121,7 +14114,7 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
@@ -14130,7 +14123,7 @@
         <v>21</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>21</v>
@@ -14138,10 +14131,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14164,17 +14157,17 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14223,7 +14216,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14238,7 +14231,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
@@ -14247,7 +14240,7 @@
         <v>21</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>21</v>
@@ -14255,10 +14248,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14281,19 +14274,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14342,7 +14335,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14357,7 +14350,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>21</v>
@@ -14366,7 +14359,7 @@
         <v>21</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>21</v>
@@ -14374,10 +14367,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14400,19 +14393,19 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14461,7 +14454,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14476,7 +14469,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
@@ -14485,7 +14478,7 @@
         <v>21</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>21</v>
@@ -14493,10 +14486,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14519,19 +14512,19 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14580,7 +14573,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14595,16 +14588,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>21</v>
@@ -14612,10 +14605,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14638,19 +14631,19 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -14699,7 +14692,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14714,16 +14707,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>21</v>
@@ -14731,10 +14724,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14757,19 +14750,19 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -14818,7 +14811,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14830,13 +14823,13 @@
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
@@ -14850,10 +14843,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14876,13 +14869,13 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14933,7 +14926,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14948,7 +14941,7 @@
         <v>21</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>21</v>
@@ -14965,14 +14958,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14994,13 +14987,13 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15050,7 +15043,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15065,7 +15058,7 @@
         <v>141</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>21</v>
@@ -15082,14 +15075,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15111,16 +15104,16 @@
         <v>135</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -15169,7 +15162,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15201,10 +15194,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15227,17 +15220,17 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15262,14 +15255,14 @@
         <v>21</v>
       </c>
       <c r="X109" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="Y109" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>21</v>
       </c>
@@ -15286,7 +15279,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15301,16 +15294,16 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15318,10 +15311,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15344,17 +15337,17 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15403,7 +15396,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15418,16 +15411,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>21</v>
@@ -15435,10 +15428,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15461,19 +15454,19 @@
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M111" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>21</v>
@@ -15522,7 +15515,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15537,16 +15530,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>21</v>
@@ -15554,10 +15547,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15580,17 +15573,17 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>21</v>
@@ -15639,7 +15632,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15654,16 +15647,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>21</v>
@@ -15671,10 +15664,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15700,14 +15693,14 @@
         <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15732,13 +15725,13 @@
         <v>21</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>21</v>
@@ -15756,7 +15749,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15771,16 +15764,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -15788,10 +15781,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15814,17 +15807,17 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -15873,7 +15866,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15882,22 +15875,22 @@
         <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>21</v>
@@ -15905,10 +15898,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15931,13 +15924,13 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15988,7 +15981,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16003,10 +15996,10 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>21</v>
@@ -16020,10 +16013,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16046,19 +16039,19 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16107,7 +16100,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16122,10 +16115,10 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -16139,10 +16132,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16165,13 +16158,13 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16222,7 +16215,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16237,7 +16230,7 @@
         <v>21</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>21</v>
@@ -16254,14 +16247,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16283,13 +16276,13 @@
         <v>135</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16339,7 +16332,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16354,7 +16347,7 @@
         <v>141</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>21</v>
@@ -16371,14 +16364,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16400,16 +16393,16 @@
         <v>135</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16458,7 +16451,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16490,10 +16483,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16516,19 +16509,19 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>21</v>
@@ -16553,13 +16546,13 @@
         <v>21</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y120" t="s" s="2">
         <v>115</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -16577,7 +16570,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>90</v>
@@ -16592,16 +16585,16 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>21</v>
@@ -16609,10 +16602,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16635,13 +16628,13 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16692,7 +16685,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16707,7 +16700,7 @@
         <v>21</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>21</v>
@@ -16724,14 +16717,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16753,13 +16746,13 @@
         <v>135</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16800,7 +16793,7 @@
         <v>138</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>21</v>
@@ -16809,7 +16802,7 @@
         <v>139</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16824,7 +16817,7 @@
         <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>21</v>
@@ -16841,10 +16834,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16867,19 +16860,19 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -16928,7 +16921,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16943,7 +16936,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
@@ -16952,7 +16945,7 @@
         <v>21</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>21</v>
@@ -16960,10 +16953,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16986,13 +16979,13 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17043,7 +17036,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17058,7 +17051,7 @@
         <v>21</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>21</v>
@@ -17075,14 +17068,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17104,13 +17097,13 @@
         <v>135</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17151,7 +17144,7 @@
         <v>138</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>21</v>
@@ -17160,7 +17153,7 @@
         <v>139</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17175,7 +17168,7 @@
         <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>21</v>
@@ -17192,10 +17185,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17221,16 +17214,16 @@
         <v>104</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17279,7 +17272,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17294,7 +17287,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>21</v>
@@ -17303,7 +17296,7 @@
         <v>21</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>21</v>
@@ -17311,10 +17304,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17337,16 +17330,16 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17396,7 +17389,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17411,7 +17404,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>21</v>
@@ -17420,7 +17413,7 @@
         <v>21</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>21</v>
@@ -17428,10 +17421,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17457,14 +17450,14 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -17513,7 +17506,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17528,7 +17521,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>21</v>
@@ -17537,7 +17530,7 @@
         <v>21</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>21</v>
@@ -17545,10 +17538,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17571,17 +17564,17 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17630,7 +17623,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17645,7 +17638,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>21</v>
@@ -17654,7 +17647,7 @@
         <v>21</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>21</v>
@@ -17662,10 +17655,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17688,19 +17681,19 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -17749,7 +17742,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17764,7 +17757,7 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>21</v>
@@ -17773,7 +17766,7 @@
         <v>21</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>21</v>
@@ -17781,10 +17774,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17807,19 +17800,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
@@ -17868,7 +17861,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -17883,7 +17876,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>21</v>
@@ -17892,7 +17885,7 @@
         <v>21</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>21</v>
@@ -17900,10 +17893,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17926,26 +17919,26 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>21</v>
@@ -17987,7 +17980,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18002,16 +17995,16 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>21</v>
@@ -18019,14 +18012,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18045,16 +18038,16 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18104,7 +18097,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18119,16 +18112,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>21</v>
@@ -18136,10 +18129,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18162,19 +18155,19 @@
         <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -18223,7 +18216,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18238,10 +18231,10 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>21</v>
@@ -18255,10 +18248,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18281,19 +18274,19 @@
         <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -18342,7 +18335,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18357,10 +18350,10 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>21</v>
@@ -18374,10 +18367,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18400,13 +18393,13 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18457,7 +18450,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18472,7 +18465,7 @@
         <v>21</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>21</v>
@@ -18489,14 +18482,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18518,13 +18511,13 @@
         <v>135</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18574,7 +18567,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18589,7 +18582,7 @@
         <v>141</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>21</v>
@@ -18606,14 +18599,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18635,16 +18628,16 @@
         <v>135</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>21</v>
@@ -18693,7 +18686,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18725,10 +18718,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18751,16 +18744,16 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18810,7 +18803,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>90</v>
@@ -18825,16 +18818,16 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>21</v>
@@ -18842,10 +18835,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18871,10 +18864,10 @@
         <v>110</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18901,13 +18894,13 @@
         <v>21</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>21</v>
@@ -18925,7 +18918,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>90</v>
@@ -18940,10 +18933,10 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>21</v>
